--- a/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5986222-667F-4EAC-B112-CEEB22CD6221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48B4D97A-79C5-40EA-B9D7-7B4891BE107B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -729,10 +729,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>SaD,WaP,FaP,SaP,FaD,RaP,RaD,WaD</t>
-  </si>
-  <si>
-    <t>FaP,SaP,FaN,RaN,SaN,WaN,RaP,WaP</t>
+    <t>FaP,SaP,RaP,SaD,WaP,RaD,WaD,FaD</t>
+  </si>
+  <si>
+    <t>FaP,SaP,RaN,FaN,WaP,RaP,SaN,WaN</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>FaP,SaP,FaN,RaN,SaN,WaN,RaP,WaP</v>
+        <v>FaP,SaP,RaN,FaN,WaP,RaP,SaN,WaN</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>SaD,WaP,FaP,SaP,FaD,RaP,RaD,WaD</v>
+        <v>FaP,SaP,RaP,SaD,WaP,RaD,WaD,FaD</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1455,7 +1455,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FEE2523-9E00-4F73-89A8-174D1F170CC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB6A3009-0ED7-43AB-941B-3FBFA2CE9543}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1539,7 +1539,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{691AEC4F-1FA7-4C3A-A115-62511848135C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBEAA2C-9240-4AB5-AC4F-18D93D4F1152}">
   <dimension ref="B9:O418"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13361,7 +13361,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A4C341A-DB1B-4F97-9806-DC0F8D839747}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7C08FC1-DA7E-4533-A340-44485FCDFF4D}">
   <dimension ref="B9:BL86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21044,7 +21044,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201A476E-3922-4F59-AB37-9D5FB88BC766}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A04E4954-B782-47C6-8450-847567A995D0}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21242,7 +21242,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA4BF6B-A258-4E03-B696-C71F60B75B80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD87752-5B99-46BE-84BE-CC460218D760}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21533,7 +21533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D9D969-05EE-4702-A912-3F21E1FB3E78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7F5DD4F-15E3-4EBE-8EA6-ECC756806CC8}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21692,7 +21692,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E46F92C-7AED-49AD-B5D5-E2F2F4C5BE4F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56164D9-84BA-4671-B6B3-C6E235E6B10A}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21962,7 +21962,7 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>0.33889999999999998</v>
+        <v>0.33890000000000003</v>
       </c>
       <c r="E28" t="s">
         <v>236</v>
@@ -22466,7 +22466,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.20440000000000003</v>
+        <v>0.2044</v>
       </c>
       <c r="E64" t="s">
         <v>236</v>
@@ -22592,7 +22592,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.1618333333333333</v>
+        <v>0.16183333333333336</v>
       </c>
       <c r="E73" t="s">
         <v>236</v>
@@ -22760,7 +22760,7 @@
         <v>43</v>
       </c>
       <c r="D85">
-        <v>0.16566666666666666</v>
+        <v>0.16566666666666668</v>
       </c>
       <c r="E85" t="s">
         <v>236</v>
@@ -22816,7 +22816,7 @@
         <v>43</v>
       </c>
       <c r="D89">
-        <v>0.21050000000000002</v>
+        <v>0.21049999999999999</v>
       </c>
       <c r="E89" t="s">
         <v>236</v>
@@ -22872,7 +22872,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.17826666666666666</v>
+        <v>0.17826666666666668</v>
       </c>
       <c r="E93" t="s">
         <v>236</v>
